--- a/data/availability/projects/naia-developments/naia-bay.xlsx
+++ b/data/availability/projects/naia-developments/naia-bay.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for naia-bay</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1019,6 @@
       <c r="G2" t="n">
         <v>65</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
